--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/43.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/43.xlsx
@@ -426,13 +426,13 @@
         <v>-5.91543056952692</v>
       </c>
       <c r="E2">
-        <v>-2.092406134321729</v>
+        <v>-6.254467724609455</v>
       </c>
       <c r="F2">
-        <v>-1.864359443786396</v>
+        <v>-2.214601465364054</v>
       </c>
       <c r="G2">
-        <v>-3.075468161741413</v>
+        <v>-3.577763994232873</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.127576763103769</v>
       </c>
       <c r="E3">
-        <v>-3.214534822578397</v>
+        <v>-6.970736458402675</v>
       </c>
       <c r="F3">
-        <v>-1.906822385221301</v>
+        <v>-2.494792597523973</v>
       </c>
       <c r="G3">
-        <v>-2.184146812384657</v>
+        <v>-3.499476213320188</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.336929371793696</v>
       </c>
       <c r="E4">
-        <v>-5.325854316122563</v>
+        <v>-7.041131586851911</v>
       </c>
       <c r="F4">
-        <v>-1.764828615237827</v>
+        <v>-2.642405183600637</v>
       </c>
       <c r="G4">
-        <v>-2.216749064855399</v>
+        <v>-3.423677962653035</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.650102384311442</v>
       </c>
       <c r="E5">
-        <v>-4.504212520644861</v>
+        <v>-8.218734081702541</v>
       </c>
       <c r="F5">
-        <v>-1.789827915086913</v>
+        <v>-2.851268912175101</v>
       </c>
       <c r="G5">
-        <v>-1.701717563674363</v>
+        <v>-3.269952780536978</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.062794668735043</v>
       </c>
       <c r="E6">
-        <v>-5.501070032427345</v>
+        <v>-9.435960724120287</v>
       </c>
       <c r="F6">
-        <v>-2.024230210689686</v>
+        <v>-2.789411404738451</v>
       </c>
       <c r="G6">
-        <v>-1.582504818805208</v>
+        <v>-2.808320378904385</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.592757081847413</v>
       </c>
       <c r="E7">
-        <v>-6.758178945430644</v>
+        <v>-9.737131416474412</v>
       </c>
       <c r="F7">
-        <v>-1.918245571705906</v>
+        <v>-2.66883590232176</v>
       </c>
       <c r="G7">
-        <v>-1.504783141179738</v>
+        <v>-2.448493873695461</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.241309876868693</v>
       </c>
       <c r="E8">
-        <v>-8.41281089224927</v>
+        <v>-10.57823659323708</v>
       </c>
       <c r="F8">
-        <v>-2.075722356815106</v>
+        <v>-2.713050012446184</v>
       </c>
       <c r="G8">
-        <v>-0.8769414902024965</v>
+        <v>-2.101830097550679</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.006755687736169</v>
       </c>
       <c r="E9">
-        <v>-9.217615821366454</v>
+        <v>-10.90512448948077</v>
       </c>
       <c r="F9">
-        <v>-1.955423529110951</v>
+        <v>-2.573489985892135</v>
       </c>
       <c r="G9">
-        <v>-0.7471250679710554</v>
+        <v>-1.974377404834277</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.883636731162585</v>
       </c>
       <c r="E10">
-        <v>-9.607961223879624</v>
+        <v>-11.70248913580335</v>
       </c>
       <c r="F10">
-        <v>-2.221436324804553</v>
+        <v>-2.82323530252956</v>
       </c>
       <c r="G10">
-        <v>-0.01954992207773027</v>
+        <v>-1.792234499809116</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.856135634204864</v>
       </c>
       <c r="E11">
-        <v>-9.884098511919346</v>
+        <v>-12.73456911841749</v>
       </c>
       <c r="F11">
-        <v>-1.957875496623237</v>
+        <v>-2.97843656238327</v>
       </c>
       <c r="G11">
-        <v>0.1973106740177681</v>
+        <v>-0.8249857885091745</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.909489923255056</v>
       </c>
       <c r="E12">
-        <v>-10.90447238922366</v>
+        <v>-13.54041106808243</v>
       </c>
       <c r="F12">
-        <v>-2.138665853916827</v>
+        <v>-2.968670939071667</v>
       </c>
       <c r="G12">
-        <v>0.7171987455049154</v>
+        <v>-0.2199372435698152</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.016066049429421</v>
       </c>
       <c r="E13">
-        <v>-11.2660483963661</v>
+        <v>-13.69033978552838</v>
       </c>
       <c r="F13">
-        <v>-2.115314176831908</v>
+        <v>-2.774862788043083</v>
       </c>
       <c r="G13">
-        <v>1.089737745584641</v>
+        <v>0.136588647736456</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.153125980649753</v>
       </c>
       <c r="E14">
-        <v>-12.75267848597417</v>
+        <v>-15.31575401804952</v>
       </c>
       <c r="F14">
-        <v>-1.955881616284699</v>
+        <v>-2.850636039479363</v>
       </c>
       <c r="G14">
-        <v>1.587418677594357</v>
+        <v>0.7082503409122654</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.290206483818237</v>
       </c>
       <c r="E15">
-        <v>-13.27775957563755</v>
+        <v>-14.95492973759235</v>
       </c>
       <c r="F15">
-        <v>-1.990552105561469</v>
+        <v>-2.727026227266217</v>
       </c>
       <c r="G15">
-        <v>2.663594268772938</v>
+        <v>1.016240324067282</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.406179518873987</v>
       </c>
       <c r="E16">
-        <v>-13.86945451795377</v>
+        <v>-17.0162322357218</v>
       </c>
       <c r="F16">
-        <v>-1.690683105748048</v>
+        <v>-2.512098849303261</v>
       </c>
       <c r="G16">
-        <v>2.80035952609131</v>
+        <v>1.53948528873125</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.481517482153369</v>
       </c>
       <c r="E17">
-        <v>-15.16013753724993</v>
+        <v>-17.57448892596538</v>
       </c>
       <c r="F17">
-        <v>-1.42142559493768</v>
+        <v>-2.509531738721985</v>
       </c>
       <c r="G17">
-        <v>3.35829900800684</v>
+        <v>1.552363310879015</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.508230200163798</v>
       </c>
       <c r="E18">
-        <v>-16.67883827978032</v>
+        <v>-17.95781972224066</v>
       </c>
       <c r="F18">
-        <v>-1.141529361573158</v>
+        <v>-2.24700968326378</v>
       </c>
       <c r="G18">
-        <v>3.443383338911649</v>
+        <v>1.933940100280951</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.488672452982811</v>
       </c>
       <c r="E19">
-        <v>-17.1429887516705</v>
+        <v>-18.95861700640982</v>
       </c>
       <c r="F19">
-        <v>-0.696632281979808</v>
+        <v>-1.900096041910569</v>
       </c>
       <c r="G19">
-        <v>4.104436382738859</v>
+        <v>2.981641689276261</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.435874039891936</v>
       </c>
       <c r="E20">
-        <v>-17.8113643443586</v>
+        <v>-19.44204066367665</v>
       </c>
       <c r="F20">
-        <v>-0.7010458235019238</v>
+        <v>-1.62029258569516</v>
       </c>
       <c r="G20">
-        <v>3.739395768305582</v>
+        <v>2.33681031859148</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.371303836576835</v>
       </c>
       <c r="E21">
-        <v>-19.35211422683233</v>
+        <v>-20.48542824588795</v>
       </c>
       <c r="F21">
-        <v>-0.414471292136032</v>
+        <v>-1.175896668380504</v>
       </c>
       <c r="G21">
-        <v>4.355978253903762</v>
+        <v>2.114576707085744</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.317395757111593</v>
       </c>
       <c r="E22">
-        <v>-19.3360970142672</v>
+        <v>-19.96094944326758</v>
       </c>
       <c r="F22">
-        <v>0.0233763808594943</v>
+        <v>-1.080174673150007</v>
       </c>
       <c r="G22">
-        <v>3.816389125912412</v>
+        <v>2.463567796744634</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.299358142593372</v>
       </c>
       <c r="E23">
-        <v>-18.2196153330981</v>
+        <v>-20.76134363870129</v>
       </c>
       <c r="F23">
-        <v>0.3134739587894924</v>
+        <v>-0.6230442637521139</v>
       </c>
       <c r="G23">
-        <v>3.904618475079528</v>
+        <v>1.829707573976998</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.333809821030963</v>
       </c>
       <c r="E24">
-        <v>-19.95268044972957</v>
+        <v>-21.73970233416244</v>
       </c>
       <c r="F24">
-        <v>0.4463358065245051</v>
+        <v>-0.2118733345963429</v>
       </c>
       <c r="G24">
-        <v>2.96624765251865</v>
+        <v>1.650415048661149</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.435392997600187</v>
       </c>
       <c r="E25">
-        <v>-20.38991820059217</v>
+        <v>-21.81995142205237</v>
       </c>
       <c r="F25">
-        <v>0.6384391774381272</v>
+        <v>-0.650126907619241</v>
       </c>
       <c r="G25">
-        <v>3.009162254344222</v>
+        <v>1.662240317327425</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.603167619687759</v>
       </c>
       <c r="E26">
-        <v>-20.67989450519933</v>
+        <v>-22.00944994537734</v>
       </c>
       <c r="F26">
-        <v>0.7888980339108098</v>
+        <v>-0.2298108023365634</v>
       </c>
       <c r="G26">
-        <v>2.616478584658031</v>
+        <v>1.293574655528647</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.833176483930372</v>
       </c>
       <c r="E27">
-        <v>-20.47382629548029</v>
+        <v>-22.65793648022375</v>
       </c>
       <c r="F27">
-        <v>1.141000568675157</v>
+        <v>0.1716997061677598</v>
       </c>
       <c r="G27">
-        <v>2.292488734911717</v>
+        <v>0.9840849952443406</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.10528323246695</v>
       </c>
       <c r="E28">
-        <v>-20.29195372238424</v>
+        <v>-20.80244859726892</v>
       </c>
       <c r="F28">
-        <v>1.153407855634287</v>
+        <v>0.2077983008469566</v>
       </c>
       <c r="G28">
-        <v>2.252282159337268</v>
+        <v>0.5013478657988947</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.40103528513142</v>
       </c>
       <c r="E29">
-        <v>-20.22348772386227</v>
+        <v>-21.16320947908997</v>
       </c>
       <c r="F29">
-        <v>1.190445818948259</v>
+        <v>0.2774449469721307</v>
       </c>
       <c r="G29">
-        <v>1.567230970895882</v>
+        <v>0.1824264612732049</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.692759227116449</v>
       </c>
       <c r="E30">
-        <v>-19.79524805085291</v>
+        <v>-21.10466989559282</v>
       </c>
       <c r="F30">
-        <v>1.25709128997309</v>
+        <v>0.02042159433370846</v>
       </c>
       <c r="G30">
-        <v>0.6746979618717518</v>
+        <v>-0.1324560776945741</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.95935532458198</v>
       </c>
       <c r="E31">
-        <v>-18.36064559911897</v>
+        <v>-20.52286514050936</v>
       </c>
       <c r="F31">
-        <v>1.356263435436247</v>
+        <v>0.3499312365541014</v>
       </c>
       <c r="G31">
-        <v>0.9972543453995614</v>
+        <v>-0.4050596395803207</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.175600180446162</v>
       </c>
       <c r="E32">
-        <v>-18.90094236144813</v>
+        <v>-20.07814182211208</v>
       </c>
       <c r="F32">
-        <v>1.276117232480589</v>
+        <v>-0.2454512072688209</v>
       </c>
       <c r="G32">
-        <v>0.4271684719004452</v>
+        <v>-0.9326281767185771</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.326830842688865</v>
       </c>
       <c r="E33">
-        <v>-18.36228037823574</v>
+        <v>-21.59843658749316</v>
       </c>
       <c r="F33">
-        <v>1.270971414174399</v>
+        <v>-0.0258849718501867</v>
       </c>
       <c r="G33">
-        <v>0.9820225253733746</v>
+        <v>-1.124954319822537</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.399222953799192</v>
       </c>
       <c r="E34">
-        <v>-17.64634675151909</v>
+        <v>-20.04545982519872</v>
       </c>
       <c r="F34">
-        <v>1.159551028293449</v>
+        <v>0.05669414616749321</v>
       </c>
       <c r="G34">
-        <v>0.7895043706281373</v>
+        <v>-1.212455348971013</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.390556781032336</v>
       </c>
       <c r="E35">
-        <v>-17.94039415425915</v>
+        <v>-20.25952984848931</v>
       </c>
       <c r="F35">
-        <v>1.138076431743274</v>
+        <v>0.06925882293315612</v>
       </c>
       <c r="G35">
-        <v>0.366092217246431</v>
+        <v>-1.077616829156498</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.299583814472824</v>
       </c>
       <c r="E36">
-        <v>-17.21081170688338</v>
+        <v>-20.53292288128039</v>
       </c>
       <c r="F36">
-        <v>1.165248539289904</v>
+        <v>-0.06873227575999113</v>
       </c>
       <c r="G36">
-        <v>-0.009237572722900525</v>
+        <v>-1.01419339771514</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.13598450984779</v>
       </c>
       <c r="E37">
-        <v>-16.27811361484157</v>
+        <v>-18.88664144053191</v>
       </c>
       <c r="F37">
-        <v>0.9028880154752442</v>
+        <v>-0.1026348684543665</v>
       </c>
       <c r="G37">
-        <v>0.6169852214856372</v>
+        <v>-0.7518525270011347</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.909755322197359</v>
       </c>
       <c r="E38">
-        <v>-16.60548152933007</v>
+        <v>-18.56586245572457</v>
       </c>
       <c r="F38">
-        <v>0.9301114818008471</v>
+        <v>0.1525958971243976</v>
       </c>
       <c r="G38">
-        <v>0.6426419494149889</v>
+        <v>-0.8813279630420308</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.64043859105377</v>
       </c>
       <c r="E39">
-        <v>-16.44843857921807</v>
+        <v>-18.00762840785103</v>
       </c>
       <c r="F39">
-        <v>0.8112788643996469</v>
+        <v>-0.1509924723275932</v>
       </c>
       <c r="G39">
-        <v>1.4515903046636</v>
+        <v>-0.08706849835116613</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.344244994347155</v>
       </c>
       <c r="E40">
-        <v>-14.9707205264571</v>
+        <v>-17.2004913146199</v>
       </c>
       <c r="F40">
-        <v>0.9107591625366451</v>
+        <v>-0.3100820887700439</v>
       </c>
       <c r="G40">
-        <v>0.7380452507657059</v>
+        <v>0.523703979825593</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.044596147932251</v>
       </c>
       <c r="E41">
-        <v>-15.11527394525594</v>
+        <v>-17.08760551455669</v>
       </c>
       <c r="F41">
-        <v>0.9302837822206295</v>
+        <v>-0.3421117427666896</v>
       </c>
       <c r="G41">
-        <v>1.367234293777431</v>
+        <v>-0.06447071450010101</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.757745651644075</v>
       </c>
       <c r="E42">
-        <v>-13.95987002999091</v>
+        <v>-17.32297747957936</v>
       </c>
       <c r="F42">
-        <v>0.6448084943982526</v>
+        <v>-0.6355758058216648</v>
       </c>
       <c r="G42">
-        <v>1.771422109212589</v>
+        <v>0.2648855295653716</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.505488199664689</v>
       </c>
       <c r="E43">
-        <v>-14.2506252321274</v>
+        <v>-16.10769355251091</v>
       </c>
       <c r="F43">
-        <v>0.1319314438941611</v>
+        <v>-0.72935030928818</v>
       </c>
       <c r="G43">
-        <v>1.382449561075921</v>
+        <v>0.1899778156482824</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.298800509202668</v>
       </c>
       <c r="E44">
-        <v>-13.81387202798362</v>
+        <v>-15.59585824931996</v>
       </c>
       <c r="F44">
-        <v>0.5153123034208142</v>
+        <v>-0.6719734411332723</v>
       </c>
       <c r="G44">
-        <v>1.705820338806391</v>
+        <v>0.8388182569811209</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.152236106782914</v>
       </c>
       <c r="E45">
-        <v>-12.42012546874688</v>
+        <v>-14.66943662225278</v>
       </c>
       <c r="F45">
-        <v>0.3082378484363967</v>
+        <v>-0.6633426811635043</v>
       </c>
       <c r="G45">
-        <v>1.963370850125072</v>
+        <v>0.516367810910568</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.067345868501021</v>
       </c>
       <c r="E46">
-        <v>-11.70767876701614</v>
+        <v>-14.27153319662081</v>
       </c>
       <c r="F46">
-        <v>0.2341503246648145</v>
+        <v>-0.738514537865351</v>
       </c>
       <c r="G46">
-        <v>1.446687386719939</v>
+        <v>1.083149759961492</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.047824606973803</v>
       </c>
       <c r="E47">
-        <v>-11.07787218745137</v>
+        <v>-14.60268691537972</v>
       </c>
       <c r="F47">
-        <v>0.07494639352077752</v>
+        <v>-0.8256944084381793</v>
       </c>
       <c r="G47">
-        <v>2.09265758507023</v>
+        <v>0.7995982239773751</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.085499278216461</v>
       </c>
       <c r="E48">
-        <v>-10.37855806034286</v>
+        <v>-13.76063075907544</v>
       </c>
       <c r="F48">
-        <v>0.1792303942266101</v>
+        <v>-0.8462478604364407</v>
       </c>
       <c r="G48">
-        <v>1.809728431647496</v>
+        <v>0.5282890853974835</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.174487400818738</v>
       </c>
       <c r="E49">
-        <v>-10.33932789001442</v>
+        <v>-13.21451943612043</v>
       </c>
       <c r="F49">
-        <v>0.07060409159530251</v>
+        <v>-1.151014168335212</v>
       </c>
       <c r="G49">
-        <v>1.76950861389089</v>
+        <v>0.6012369563553241</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.302221081273784</v>
       </c>
       <c r="E50">
-        <v>-9.84278524354737</v>
+        <v>-12.5014296910806</v>
       </c>
       <c r="F50">
-        <v>-0.02962753577603487</v>
+        <v>-0.8610242781675783</v>
       </c>
       <c r="G50">
-        <v>1.987468311105427</v>
+        <v>0.9819066562795001</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.458801435346373</v>
       </c>
       <c r="E51">
-        <v>-9.074493400354031</v>
+        <v>-11.64993166647032</v>
       </c>
       <c r="F51">
-        <v>-0.03693787810574051</v>
+        <v>-0.83995392490997</v>
       </c>
       <c r="G51">
-        <v>2.386485054408244</v>
+        <v>0.8203586550541447</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.633154988208912</v>
       </c>
       <c r="E52">
-        <v>-9.007807092117078</v>
+        <v>-11.42599862679103</v>
       </c>
       <c r="F52">
-        <v>-0.125521831426314</v>
+        <v>-1.281100156903444</v>
       </c>
       <c r="G52">
-        <v>1.434587342773903</v>
+        <v>0.1616196825588854</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.816858971752801</v>
       </c>
       <c r="E53">
-        <v>-8.749896911958228</v>
+        <v>-10.69366286721859</v>
       </c>
       <c r="F53">
-        <v>-0.1045558524614586</v>
+        <v>-1.233124430402908</v>
       </c>
       <c r="G53">
-        <v>1.516185669225859</v>
+        <v>0.3679163278385695</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.00604643221773</v>
       </c>
       <c r="E54">
-        <v>-7.301124865054289</v>
+        <v>-10.4758749667677</v>
       </c>
       <c r="F54">
-        <v>-0.3385174566059425</v>
+        <v>-1.136052196305848</v>
       </c>
       <c r="G54">
-        <v>0.9186288888418707</v>
+        <v>-0.04268401430615733</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.198522624543571</v>
       </c>
       <c r="E55">
-        <v>-7.823642838429334</v>
+        <v>-10.1306150514749</v>
       </c>
       <c r="F55">
-        <v>-0.3668260842292128</v>
+        <v>-0.9650001261995694</v>
       </c>
       <c r="G55">
-        <v>1.000899256038299</v>
+        <v>-0.319157603927312</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.397284592758551</v>
       </c>
       <c r="E56">
-        <v>-7.044736252162017</v>
+        <v>-10.42805880972071</v>
       </c>
       <c r="F56">
-        <v>-0.3355825508978239</v>
+        <v>-1.089922900746152</v>
       </c>
       <c r="G56">
-        <v>0.6009820443488003</v>
+        <v>-0.1906521577294223</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.600413980512118</v>
       </c>
       <c r="E57">
-        <v>-6.429063039975185</v>
+        <v>-9.311853365466074</v>
       </c>
       <c r="F57">
-        <v>-0.3233003474165156</v>
+        <v>-1.227894946989035</v>
       </c>
       <c r="G57">
-        <v>0.3867136054105513</v>
+        <v>-0.7529119015737015</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.810606106288112</v>
       </c>
       <c r="E58">
-        <v>-5.949429715452779</v>
+        <v>-9.589937897329095</v>
       </c>
       <c r="F58">
-        <v>-0.1673237356737855</v>
+        <v>-1.157900386554685</v>
       </c>
       <c r="G58">
-        <v>0.3064030811733715</v>
+        <v>-1.297490021692733</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.022134527356767</v>
       </c>
       <c r="E59">
-        <v>-6.021255841688439</v>
+        <v>-8.966471181375063</v>
       </c>
       <c r="F59">
-        <v>-0.5672620028475952</v>
+        <v>-1.109299242665035</v>
       </c>
       <c r="G59">
-        <v>0.03019764574089786</v>
+        <v>-0.8326761857969014</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.23537938374562</v>
       </c>
       <c r="E60">
-        <v>-5.36850801280081</v>
+        <v>-8.634149116322174</v>
       </c>
       <c r="F60">
-        <v>-0.5818180748495881</v>
+        <v>-1.141420845443391</v>
       </c>
       <c r="G60">
-        <v>-0.570964318735357</v>
+        <v>-1.477457898298594</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.4403226732431</v>
       </c>
       <c r="E61">
-        <v>-5.363114600257675</v>
+        <v>-9.497538913676589</v>
       </c>
       <c r="F61">
-        <v>-0.7164344047437302</v>
+        <v>-1.329015412583576</v>
       </c>
       <c r="G61">
-        <v>-0.5890034813788457</v>
+        <v>-2.259117426666992</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.636225656347009</v>
       </c>
       <c r="E62">
-        <v>-4.910715518417399</v>
+        <v>-7.763975664904269</v>
       </c>
       <c r="F62">
-        <v>-0.4695444705437543</v>
+        <v>-1.143552234770794</v>
       </c>
       <c r="G62">
-        <v>-0.7571692631372042</v>
+        <v>-2.13135023212436</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.813268863715877</v>
       </c>
       <c r="E63">
-        <v>-5.323698762494913</v>
+        <v>-7.487657237904239</v>
       </c>
       <c r="F63">
-        <v>-0.501156627369389</v>
+        <v>-1.320563579972812</v>
       </c>
       <c r="G63">
-        <v>-1.012428876942709</v>
+        <v>-1.825988822127525</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.972723386478878</v>
       </c>
       <c r="E64">
-        <v>-4.769304860579877</v>
+        <v>-8.120968856350945</v>
       </c>
       <c r="F64">
-        <v>-0.6731836859087624</v>
+        <v>-1.178823290414595</v>
       </c>
       <c r="G64">
-        <v>-1.311669088237432</v>
+        <v>-2.920339308316705</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.106912831573182</v>
       </c>
       <c r="E65">
-        <v>-4.530790134595879</v>
+        <v>-7.999071393012476</v>
       </c>
       <c r="F65">
-        <v>-0.7982870445491549</v>
+        <v>-1.234470527432457</v>
       </c>
       <c r="G65">
-        <v>-1.423846923835636</v>
+        <v>-2.127933749127832</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.220260860945353</v>
       </c>
       <c r="E66">
-        <v>-4.846710066792986</v>
+        <v>-7.048114493771739</v>
       </c>
       <c r="F66">
-        <v>-0.7437075731135011</v>
+        <v>-1.299359031195951</v>
       </c>
       <c r="G66">
-        <v>-1.678500707807454</v>
+        <v>-2.759936755847937</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.308838232036526</v>
       </c>
       <c r="E67">
-        <v>-4.396584278904561</v>
+        <v>-7.203096988210249</v>
       </c>
       <c r="F67">
-        <v>-0.9264238846185993</v>
+        <v>-1.430682600663965</v>
       </c>
       <c r="G67">
-        <v>-1.891944820906425</v>
+        <v>-2.63069305799479</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.382617896646158</v>
       </c>
       <c r="E68">
-        <v>-4.182088579057246</v>
+        <v>-7.559700730892267</v>
       </c>
       <c r="F68">
-        <v>-0.8394196279351643</v>
+        <v>-1.240885404599736</v>
       </c>
       <c r="G68">
-        <v>-2.308176401013452</v>
+        <v>-2.524202739633054</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.443336821997527</v>
       </c>
       <c r="E69">
-        <v>-4.276403107214997</v>
+        <v>-7.339462926003226</v>
       </c>
       <c r="F69">
-        <v>-1.255282430060392</v>
+        <v>-1.599843507989652</v>
       </c>
       <c r="G69">
-        <v>-2.507014387193158</v>
+        <v>-3.048540184324982</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.50647198368744</v>
       </c>
       <c r="E70">
-        <v>-4.533131355657845</v>
+        <v>-7.858747568936794</v>
       </c>
       <c r="F70">
-        <v>-1.317078638309235</v>
+        <v>-1.834932520169346</v>
       </c>
       <c r="G70">
-        <v>-2.19653487379261</v>
+        <v>-3.35047849023421</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.576459117939842</v>
       </c>
       <c r="E71">
-        <v>-3.880424283036285</v>
+        <v>-7.237332251708237</v>
       </c>
       <c r="F71">
-        <v>-1.365403935853752</v>
+        <v>-1.618491714961474</v>
       </c>
       <c r="G71">
-        <v>-1.695265310418323</v>
+        <v>-3.173076286421285</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.668002313217379</v>
       </c>
       <c r="E72">
-        <v>-3.62994985719803</v>
+        <v>-7.676123269155464</v>
       </c>
       <c r="F72">
-        <v>-1.21529713552726</v>
+        <v>-1.862444258351123</v>
       </c>
       <c r="G72">
-        <v>-2.836125650888724</v>
+        <v>-3.102250475154117</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.781040021086867</v>
       </c>
       <c r="E73">
-        <v>-4.310602142920923</v>
+        <v>-7.174775911766279</v>
       </c>
       <c r="F73">
-        <v>-1.290384498754021</v>
+        <v>-1.753414540794652</v>
       </c>
       <c r="G73">
-        <v>-1.925520373765713</v>
+        <v>-2.15860264300364</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.922591337744054</v>
       </c>
       <c r="E74">
-        <v>-4.563050983426523</v>
+        <v>-8.086430185094445</v>
       </c>
       <c r="F74">
-        <v>-1.48353741116699</v>
+        <v>-1.969288742699009</v>
       </c>
       <c r="G74">
-        <v>-1.787937411699142</v>
+        <v>-3.309060254992388</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.082091862766545</v>
       </c>
       <c r="E75">
-        <v>-5.640891195888175</v>
+        <v>-7.428139504021427</v>
       </c>
       <c r="F75">
-        <v>-1.472366048372836</v>
+        <v>-1.92434815436233</v>
       </c>
       <c r="G75">
-        <v>-1.771285367636608</v>
+        <v>-3.421208295680739</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.253400763993907</v>
       </c>
       <c r="E76">
-        <v>-6.063316308271681</v>
+        <v>-8.685737492217555</v>
       </c>
       <c r="F76">
-        <v>-1.635030898525769</v>
+        <v>-1.738532092035956</v>
       </c>
       <c r="G76">
-        <v>-1.747946021584746</v>
+        <v>-2.818096419881853</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.414704457704086</v>
       </c>
       <c r="E77">
-        <v>-6.094526551132545</v>
+        <v>-8.42391018204207</v>
       </c>
       <c r="F77">
-        <v>-1.484591094503351</v>
+        <v>-1.917288807355673</v>
       </c>
       <c r="G77">
-        <v>-1.174880657100285</v>
+        <v>-2.426088101485674</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.554904312175674</v>
       </c>
       <c r="E78">
-        <v>-6.487054678117412</v>
+        <v>-8.733386095726262</v>
       </c>
       <c r="F78">
-        <v>-1.528967564638723</v>
+        <v>-1.912963072778254</v>
       </c>
       <c r="G78">
-        <v>-0.9827233518188287</v>
+        <v>-2.659203476178993</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.655006173191538</v>
       </c>
       <c r="E79">
-        <v>-6.680379761978867</v>
+        <v>-9.39748680895112</v>
       </c>
       <c r="F79">
-        <v>-1.482665968659245</v>
+        <v>-2.300876758733026</v>
       </c>
       <c r="G79">
-        <v>-0.8279023791292723</v>
+        <v>-2.878861483255176</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.709965173141963</v>
       </c>
       <c r="E80">
-        <v>-7.089568144837953</v>
+        <v>-10.49149820209416</v>
       </c>
       <c r="F80">
-        <v>-1.742480091077699</v>
+        <v>-2.36814433367736</v>
       </c>
       <c r="G80">
-        <v>-1.007506095725813</v>
+        <v>-2.651294582885674</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.709248744893688</v>
       </c>
       <c r="E81">
-        <v>-9.151717467606835</v>
+        <v>-10.86337648760405</v>
       </c>
       <c r="F81">
-        <v>-1.603581101711083</v>
+        <v>-2.4285488846895</v>
       </c>
       <c r="G81">
-        <v>-0.5694811943337635</v>
+        <v>-1.95996660010183</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.654948913283015</v>
       </c>
       <c r="E82">
-        <v>-9.195580266845129</v>
+        <v>-11.20315694934757</v>
       </c>
       <c r="F82">
-        <v>-1.830335909451211</v>
+        <v>-1.99224197506318</v>
       </c>
       <c r="G82">
-        <v>-0.3174361202468909</v>
+        <v>-2.041895981107713</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.545033637522908</v>
       </c>
       <c r="E83">
-        <v>-9.445257681258035</v>
+        <v>-11.84380922416072</v>
       </c>
       <c r="F83">
-        <v>-1.848284145967668</v>
+        <v>-2.424870105053667</v>
       </c>
       <c r="G83">
-        <v>-0.4339871865024724</v>
+        <v>-1.765541571125972</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.387268846336195</v>
       </c>
       <c r="E84">
-        <v>-11.11415884967483</v>
+        <v>-13.9548434238424</v>
       </c>
       <c r="F84">
-        <v>-1.875623583729663</v>
+        <v>-2.658810171645678</v>
       </c>
       <c r="G84">
-        <v>0.2988550373438332</v>
+        <v>-1.540285431542882</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.186712936882663</v>
       </c>
       <c r="E85">
-        <v>-11.20193878983951</v>
+        <v>-14.50727196803811</v>
       </c>
       <c r="F85">
-        <v>-2.257347708450717</v>
+        <v>-2.59049968214122</v>
       </c>
       <c r="G85">
-        <v>-0.1181743842381582</v>
+        <v>-2.004973466708222</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.954812938859422</v>
       </c>
       <c r="E86">
-        <v>-13.62331384174085</v>
+        <v>-15.81142719750709</v>
       </c>
       <c r="F86">
-        <v>-2.018985816662562</v>
+        <v>-2.751103554195988</v>
       </c>
       <c r="G86">
-        <v>0.2683814656548419</v>
+        <v>-1.197319534765465</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.701835896345892</v>
       </c>
       <c r="E87">
-        <v>-13.92202104423481</v>
+        <v>-16.30686942479027</v>
       </c>
       <c r="F87">
-        <v>-2.490969681960054</v>
+        <v>-2.761509505509955</v>
       </c>
       <c r="G87">
-        <v>0.8703214083328256</v>
+        <v>-2.074064552112811</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.44106141513003</v>
       </c>
       <c r="E88">
-        <v>-15.45842359166117</v>
+        <v>-18.01114250368098</v>
       </c>
       <c r="F88">
-        <v>-2.336835359321149</v>
+        <v>-2.803727250193632</v>
       </c>
       <c r="G88">
-        <v>0.1577165493680847</v>
+        <v>-1.21006182454612</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.186228935410713</v>
       </c>
       <c r="E89">
-        <v>-17.04788626903541</v>
+        <v>-19.92145662144669</v>
       </c>
       <c r="F89">
-        <v>-2.649505120610031</v>
+        <v>-2.7100662330613</v>
       </c>
       <c r="G89">
-        <v>0.8486075401407458</v>
+        <v>-0.5394545462925738</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.949176801727347</v>
       </c>
       <c r="E90">
-        <v>-18.69024152281925</v>
+        <v>-21.41543189589519</v>
       </c>
       <c r="F90">
-        <v>-2.589997691495123</v>
+        <v>-2.940004456730387</v>
       </c>
       <c r="G90">
-        <v>1.031928999377888</v>
+        <v>-1.349005420829332</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.741573338152585</v>
       </c>
       <c r="E91">
-        <v>-21.14180338245572</v>
+        <v>-22.35156709970882</v>
       </c>
       <c r="F91">
-        <v>-2.490689693777907</v>
+        <v>-3.153164927023173</v>
       </c>
       <c r="G91">
-        <v>0.6976764584598332</v>
+        <v>-1.732273899001836</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.567425983731899</v>
       </c>
       <c r="E92">
-        <v>-22.08399768449161</v>
+        <v>-24.64051598620386</v>
       </c>
       <c r="F92">
-        <v>-2.862178510869971</v>
+        <v>-3.508446735879464</v>
       </c>
       <c r="G92">
-        <v>0.9895606375662952</v>
+        <v>-1.458286529080674</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.433216504777693</v>
       </c>
       <c r="E93">
-        <v>-24.1349345056175</v>
+        <v>-26.3012976007249</v>
       </c>
       <c r="F93">
-        <v>-2.761890554515243</v>
+        <v>-3.51207912694074</v>
       </c>
       <c r="G93">
-        <v>0.1286003013501946</v>
+        <v>-1.886224198214564</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.335663959931245</v>
       </c>
       <c r="E94">
-        <v>-26.77915123496229</v>
+        <v>-28.22866595160349</v>
       </c>
       <c r="F94">
-        <v>-2.854404282794698</v>
+        <v>-3.570025911868774</v>
       </c>
       <c r="G94">
-        <v>0.1520290321316168</v>
+        <v>-1.675541080095346</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.278170084743371</v>
       </c>
       <c r="E95">
-        <v>-28.87211229487936</v>
+        <v>-30.40737819532981</v>
       </c>
       <c r="F95">
-        <v>-2.859622997432334</v>
+        <v>-3.426888994869436</v>
       </c>
       <c r="G95">
-        <v>-0.6324378388540837</v>
+        <v>-1.884314013438404</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.257361700773732</v>
       </c>
       <c r="E96">
-        <v>-31.64998240608654</v>
+        <v>-33.03947446399307</v>
       </c>
       <c r="F96">
-        <v>-3.265151916207638</v>
+        <v>-3.683197466439242</v>
       </c>
       <c r="G96">
-        <v>-0.2627094919371989</v>
+        <v>-2.502495492532053</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.274024079648825</v>
       </c>
       <c r="E97">
-        <v>-33.68912481665945</v>
+        <v>-35.00165545880562</v>
       </c>
       <c r="F97">
-        <v>-3.336600261433901</v>
+        <v>-3.899225744680519</v>
       </c>
       <c r="G97">
-        <v>-1.099847142452704</v>
+        <v>-2.197087734897668</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.328644727878523</v>
       </c>
       <c r="E98">
-        <v>-36.03114741852438</v>
+        <v>-38.38519764735369</v>
       </c>
       <c r="F98">
-        <v>-3.428998018276963</v>
+        <v>-3.891790318872991</v>
       </c>
       <c r="G98">
-        <v>-1.581750014422254</v>
+        <v>-2.701624806719214</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.416832280994751</v>
       </c>
       <c r="E99">
-        <v>-38.65721402404643</v>
+        <v>-40.12675138851254</v>
       </c>
       <c r="F99">
-        <v>-3.477849329122258</v>
+        <v>-4.332593606761706</v>
       </c>
       <c r="G99">
-        <v>-1.574377429506297</v>
+        <v>-3.349789896762041</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.549700147202051</v>
       </c>
       <c r="E100">
-        <v>-40.67258647455308</v>
+        <v>-42.95600156581074</v>
       </c>
       <c r="F100">
-        <v>-3.686011430506552</v>
+        <v>-4.372774396001899</v>
       </c>
       <c r="G100">
-        <v>-1.481811265682735</v>
+        <v>-3.860719632019921</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.710284683559868</v>
       </c>
       <c r="E101">
-        <v>-43.21020292575731</v>
+        <v>-45.52993637855649</v>
       </c>
       <c r="F101">
-        <v>-3.958450700511073</v>
+        <v>-4.425580332828159</v>
       </c>
       <c r="G101">
-        <v>-2.675329143500783</v>
+        <v>-3.897390544958428</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.938446051715693</v>
       </c>
       <c r="E102">
-        <v>-46.19744023999811</v>
+        <v>-47.72882297398698</v>
       </c>
       <c r="F102">
-        <v>-3.950473522422114</v>
+        <v>-4.727246889905655</v>
       </c>
       <c r="G102">
-        <v>-2.684764198287706</v>
+        <v>-4.254065410813967</v>
       </c>
     </row>
   </sheetData>
